--- a/artfynd/A 8376-2026 artfynd.xlsx
+++ b/artfynd/A 8376-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68784046</v>
+        <v>68784052</v>
       </c>
       <c r="B2" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601192.9166249854</v>
+        <v>601320</v>
       </c>
       <c r="R2" t="n">
-        <v>6821627.782893091</v>
+        <v>6821673</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-08-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-08-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,15 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>grund, örtrik svacka i 150-årig barrskog</t>
+          <t>asprik, gallrad olikåldrig barrskog med kovall</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>100 substratenheter</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68784047</v>
+        <v>68784051</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601212.1992870742</v>
+        <v>601321</v>
       </c>
       <c r="R3" t="n">
-        <v>6821524.247630809</v>
+        <v>6821674</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,19 +853,9 @@
           <t>2017-08-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>kärrkant med blandskog och örnbräken</t>
+          <t>asprik, gallrad, olikåldrig barrskog</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter</t>
+          <t>1 substratenheter # äldre asp, 40 cm bred</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,6 +892,226 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>68784047</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601212</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6821524</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-08-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-08-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>kärrkant med blandskog och örnbräken</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>2 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>68784046</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>601193</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6821628</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-08-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-08-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>grund, örtrik svacka i 150-årig barrskog</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>100 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
